--- a/results/tables/excel/table_A3_robustness_instances.xlsx
+++ b/results/tables/excel/table_A3_robustness_instances.xlsx
@@ -34783,7 +34783,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -34905,7 +34905,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -35027,7 +35027,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -35149,7 +35149,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -35271,7 +35271,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -35393,7 +35393,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -35515,7 +35515,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -35637,7 +35637,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -35759,7 +35759,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -35881,7 +35881,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -36003,7 +36003,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -36125,7 +36125,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -36247,7 +36247,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -36369,7 +36369,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -36491,7 +36491,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -36613,7 +36613,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -36735,7 +36735,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -36857,7 +36857,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -36979,7 +36979,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -37223,7 +37223,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -37345,7 +37345,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -37467,7 +37467,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -37589,7 +37589,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -37711,7 +37711,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -37833,7 +37833,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -37955,7 +37955,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -38077,7 +38077,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -38199,7 +38199,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -38321,7 +38321,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -38443,7 +38443,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -38565,7 +38565,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -38687,7 +38687,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -38809,7 +38809,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -38931,7 +38931,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -39053,7 +39053,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -39175,7 +39175,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -39297,7 +39297,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -39419,7 +39419,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -39541,7 +39541,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -39663,7 +39663,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -39785,7 +39785,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -39907,7 +39907,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -40029,7 +40029,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -40151,7 +40151,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -40273,7 +40273,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -40395,7 +40395,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -40517,7 +40517,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -40639,7 +40639,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -40761,7 +40761,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -40883,7 +40883,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -41005,7 +41005,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -41127,7 +41127,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -41249,7 +41249,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -41371,7 +41371,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -41493,7 +41493,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -41615,7 +41615,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -41737,7 +41737,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -41859,7 +41859,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -41981,7 +41981,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>independent</t>
+          <t>seasonal</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">

--- a/results/tables/excel/table_A3_robustness_instances.xlsx
+++ b/results/tables/excel/table_A3_robustness_instances.xlsx
@@ -25018,7 +25018,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -25140,7 +25140,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -25262,7 +25262,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -25384,7 +25384,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -25506,7 +25506,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -25628,7 +25628,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -25750,7 +25750,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -25872,7 +25872,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -25994,7 +25994,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -26238,7 +26238,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -26360,7 +26360,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -26482,7 +26482,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -26604,7 +26604,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -26726,7 +26726,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -26848,7 +26848,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -26970,7 +26970,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -27092,7 +27092,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -27214,7 +27214,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -27458,7 +27458,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -27580,7 +27580,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -27702,7 +27702,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -27824,7 +27824,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -27946,7 +27946,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -28068,7 +28068,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -28190,7 +28190,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -28312,7 +28312,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -28556,7 +28556,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -28678,7 +28678,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -28800,7 +28800,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -28922,7 +28922,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -29044,7 +29044,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -29166,7 +29166,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -29288,7 +29288,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -29410,7 +29410,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -29532,7 +29532,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -29654,7 +29654,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -29776,7 +29776,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -30020,7 +30020,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -30142,7 +30142,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -30264,7 +30264,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -30386,7 +30386,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -30508,7 +30508,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -30630,7 +30630,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -30752,7 +30752,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -30874,7 +30874,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -30996,7 +30996,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -31118,7 +31118,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -31240,7 +31240,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -31362,7 +31362,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -31484,7 +31484,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -31606,7 +31606,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -31728,7 +31728,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -31850,7 +31850,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -31972,7 +31972,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -32094,7 +32094,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -32216,7 +32216,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -32338,7 +32338,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -32460,7 +32460,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -32582,7 +32582,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -32826,7 +32826,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -32948,7 +32948,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -33070,7 +33070,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -33192,7 +33192,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -33314,7 +33314,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -33436,7 +33436,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -33558,7 +33558,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -33680,7 +33680,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -33802,7 +33802,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -33924,7 +33924,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -34168,7 +34168,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -34290,7 +34290,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -34412,7 +34412,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -34534,7 +34534,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -34656,7 +34656,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Independent capacities, lining classes, uniform weights</t>
+          <t>Untied capacities, lining classes, uniform weights</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -42098,7 +42098,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -42220,7 +42220,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -42342,7 +42342,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -42464,7 +42464,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -42586,7 +42586,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -42830,7 +42830,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -42952,7 +42952,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -43074,7 +43074,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -43196,7 +43196,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -43318,7 +43318,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -43440,7 +43440,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -43562,7 +43562,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -43684,7 +43684,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -43806,7 +43806,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -43928,7 +43928,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -44050,7 +44050,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -44172,7 +44172,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -44294,7 +44294,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -44416,7 +44416,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -44538,7 +44538,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -44660,7 +44660,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -44782,7 +44782,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -44904,7 +44904,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -45026,7 +45026,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -45148,7 +45148,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -45270,7 +45270,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -45392,7 +45392,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -45514,7 +45514,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -45636,7 +45636,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -45758,7 +45758,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -45880,7 +45880,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -46002,7 +46002,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -46124,7 +46124,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -46246,7 +46246,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -46368,7 +46368,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -46490,7 +46490,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -46612,7 +46612,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -46734,7 +46734,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -46856,7 +46856,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -46978,7 +46978,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -47100,7 +47100,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -47222,7 +47222,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -47344,7 +47344,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -47466,7 +47466,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -47588,7 +47588,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -47710,7 +47710,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -47832,7 +47832,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -47954,7 +47954,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -48076,7 +48076,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -48198,7 +48198,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -48320,7 +48320,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -48442,7 +48442,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -48564,7 +48564,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -48686,7 +48686,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -48808,7 +48808,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -48930,7 +48930,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -49052,7 +49052,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -49174,7 +49174,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -49296,7 +49296,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Independent capacities, generic efficiencies and weights</t>
+          <t>Untied capacities, generic efficiencies and weights</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">

--- a/results/tables/excel/table_A3_robustness_instances.xlsx
+++ b/results/tables/excel/table_A3_robustness_instances.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>stage2_optimum_unique</t>
+          <t>stage2_multiplicity_not_detected</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD2" t="n">
@@ -829,7 +829,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD3" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD4" t="n">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD5" t="n">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD6" t="n">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD7" t="n">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD8" t="n">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD9" t="n">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD10" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD11" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD12" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD13" t="n">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD14" t="n">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD15" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD16" t="n">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD17" t="n">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD18" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD19" t="n">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD20" t="n">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD21" t="n">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD22" t="n">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD23" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD24" t="n">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD25" t="n">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD26" t="n">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD27" t="n">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD28" t="n">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD29" t="n">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD30" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD31" t="n">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD32" t="n">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD33" t="n">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD34" t="n">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD35" t="n">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD36" t="n">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD37" t="n">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD38" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD39" t="n">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD40" t="n">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD41" t="n">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD42" t="n">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD43" t="n">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD44" t="n">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD45" t="n">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD46" t="n">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD47" t="n">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD48" t="n">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD49" t="n">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD50" t="n">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD51" t="n">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD52" t="n">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD53" t="n">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD54" t="n">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD55" t="n">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD56" t="n">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD57" t="n">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD58" t="n">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD59" t="n">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD60" t="n">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD61" t="n">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD62" t="n">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD63" t="n">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD64" t="n">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD65" t="n">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD66" t="n">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD67" t="n">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD68" t="n">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD69" t="n">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD70" t="n">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD71" t="n">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD72" t="n">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD73" t="n">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD74" t="n">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD75" t="n">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD76" t="n">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD77" t="n">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD78" t="n">
@@ -10101,7 +10101,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD79" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD80" t="n">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD81" t="n">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD82" t="n">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD83" t="n">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD84" t="n">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD85" t="n">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD86" t="n">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD87" t="n">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD88" t="n">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD89" t="n">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD90" t="n">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD91" t="n">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD92" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD93" t="n">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD94" t="n">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD95" t="n">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD96" t="n">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD97" t="n">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD98" t="n">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD99" t="n">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD100" t="n">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD101" t="n">
@@ -12907,7 +12907,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD102" t="n">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD103" t="n">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD104" t="n">
@@ -13273,7 +13273,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD105" t="n">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD106" t="n">
@@ -13517,7 +13517,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD107" t="n">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD108" t="n">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD109" t="n">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD110" t="n">
@@ -14005,7 +14005,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD111" t="n">
@@ -14127,7 +14127,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD112" t="n">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD113" t="n">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD114" t="n">
@@ -14493,7 +14493,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD115" t="n">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD116" t="n">
@@ -14737,7 +14737,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD117" t="n">
@@ -14859,7 +14859,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD118" t="n">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD119" t="n">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD120" t="n">
@@ -15225,7 +15225,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD121" t="n">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD122" t="n">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD123" t="n">
@@ -15591,7 +15591,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD124" t="n">
@@ -15713,7 +15713,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD125" t="n">
@@ -15835,7 +15835,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD126" t="n">
@@ -15957,7 +15957,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD127" t="n">
@@ -16079,7 +16079,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD128" t="n">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD129" t="n">
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD130" t="n">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD131" t="n">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD132" t="n">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD133" t="n">
@@ -16811,7 +16811,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD134" t="n">
@@ -16933,7 +16933,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD135" t="n">
@@ -17055,7 +17055,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD136" t="n">
@@ -17177,7 +17177,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD137" t="n">
@@ -17299,7 +17299,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD138" t="n">
@@ -17421,7 +17421,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD139" t="n">
@@ -17543,7 +17543,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD140" t="n">
@@ -17665,7 +17665,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD141" t="n">
@@ -17787,7 +17787,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD142" t="n">
@@ -17909,7 +17909,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD143" t="n">
@@ -18031,7 +18031,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD144" t="n">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD145" t="n">
@@ -18275,7 +18275,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD146" t="n">
@@ -18397,7 +18397,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD147" t="n">
@@ -18519,7 +18519,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD148" t="n">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD149" t="n">
@@ -18763,7 +18763,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD150" t="n">
@@ -18885,7 +18885,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD151" t="n">
@@ -19007,7 +19007,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD152" t="n">
@@ -19129,7 +19129,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD153" t="n">
@@ -19251,7 +19251,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD154" t="n">
@@ -19373,7 +19373,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD155" t="n">
@@ -19495,7 +19495,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD156" t="n">
@@ -19617,7 +19617,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD157" t="n">
@@ -19739,7 +19739,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD158" t="n">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD159" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD160" t="n">
@@ -20105,7 +20105,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD161" t="n">
@@ -20227,7 +20227,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD162" t="n">
@@ -20349,7 +20349,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD163" t="n">
@@ -20471,7 +20471,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD164" t="n">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD165" t="n">
@@ -20715,7 +20715,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD166" t="n">
@@ -20837,7 +20837,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD167" t="n">
@@ -20959,7 +20959,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD168" t="n">
@@ -21081,7 +21081,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD169" t="n">
@@ -21203,7 +21203,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD170" t="n">
@@ -21325,7 +21325,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD171" t="n">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD172" t="n">
@@ -21569,7 +21569,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD173" t="n">
@@ -21691,7 +21691,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD174" t="n">
@@ -21813,7 +21813,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD175" t="n">
@@ -21935,7 +21935,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD176" t="n">
@@ -22057,7 +22057,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD177" t="n">
@@ -22179,7 +22179,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD178" t="n">
@@ -22301,7 +22301,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD179" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD180" t="n">
@@ -22545,7 +22545,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD181" t="n">
@@ -22667,7 +22667,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD182" t="n">
@@ -22789,7 +22789,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD183" t="n">
@@ -22911,7 +22911,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD184" t="n">
@@ -23033,7 +23033,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD185" t="n">
@@ -23155,7 +23155,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD186" t="n">
@@ -23277,7 +23277,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD187" t="n">
@@ -23399,7 +23399,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD188" t="n">
@@ -23521,7 +23521,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD189" t="n">
@@ -23643,7 +23643,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD190" t="n">
@@ -23765,7 +23765,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD191" t="n">
@@ -23887,7 +23887,7 @@
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD192" t="n">
@@ -24009,7 +24009,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD193" t="n">
@@ -24131,7 +24131,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD194" t="n">
@@ -24253,7 +24253,7 @@
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD195" t="n">
@@ -24375,7 +24375,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD196" t="n">
@@ -24497,7 +24497,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD197" t="n">
@@ -24619,7 +24619,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD198" t="n">
@@ -24741,7 +24741,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD199" t="n">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD200" t="n">
@@ -24985,7 +24985,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD201" t="n">
@@ -25107,7 +25107,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD202" t="n">
@@ -25595,7 +25595,7 @@
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD206" t="n">
@@ -25717,7 +25717,7 @@
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD207" t="n">
@@ -26083,7 +26083,7 @@
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD210" t="n">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD212" t="n">
@@ -26449,7 +26449,7 @@
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD213" t="n">
@@ -26571,7 +26571,7 @@
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD214" t="n">
@@ -26937,7 +26937,7 @@
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD217" t="n">
@@ -27059,7 +27059,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD218" t="n">
@@ -27425,7 +27425,7 @@
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD221" t="n">
@@ -27669,7 +27669,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD223" t="n">
@@ -28035,7 +28035,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD226" t="n">
@@ -28401,7 +28401,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD229" t="n">
@@ -28523,7 +28523,7 @@
       </c>
       <c r="AC230" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD230" t="n">
@@ -29011,7 +29011,7 @@
       </c>
       <c r="AC234" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD234" t="n">
@@ -29133,7 +29133,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD235" t="n">
@@ -29255,7 +29255,7 @@
       </c>
       <c r="AC236" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD236" t="n">
@@ -29743,7 +29743,7 @@
       </c>
       <c r="AC240" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD240" t="n">
@@ -29865,7 +29865,7 @@
       </c>
       <c r="AC241" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD241" t="n">
@@ -29987,7 +29987,7 @@
       </c>
       <c r="AC242" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD242" t="n">
@@ -30109,7 +30109,7 @@
       </c>
       <c r="AC243" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD243" t="n">
@@ -30475,7 +30475,7 @@
       </c>
       <c r="AC246" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD246" t="n">
@@ -30597,7 +30597,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD247" t="n">
@@ -30963,7 +30963,7 @@
       </c>
       <c r="AC250" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD250" t="n">
@@ -31085,7 +31085,7 @@
       </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD251" t="n">
@@ -31207,7 +31207,7 @@
       </c>
       <c r="AC252" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD252" t="n">
@@ -31329,7 +31329,7 @@
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD253" t="n">
@@ -31451,7 +31451,7 @@
       </c>
       <c r="AC254" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD254" t="n">
@@ -31573,7 +31573,7 @@
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD255" t="n">
@@ -32427,7 +32427,7 @@
       </c>
       <c r="AC262" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD262" t="n">
@@ -32549,7 +32549,7 @@
       </c>
       <c r="AC263" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD263" t="n">
@@ -32671,7 +32671,7 @@
       </c>
       <c r="AC264" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD264" t="n">
@@ -33159,7 +33159,7 @@
       </c>
       <c r="AC268" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD268" t="n">
@@ -33281,7 +33281,7 @@
       </c>
       <c r="AC269" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD269" t="n">
@@ -33403,7 +33403,7 @@
       </c>
       <c r="AC270" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD270" t="n">
@@ -33647,7 +33647,7 @@
       </c>
       <c r="AC272" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD272" t="n">
@@ -33891,7 +33891,7 @@
       </c>
       <c r="AC274" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD274" t="n">
@@ -34135,7 +34135,7 @@
       </c>
       <c r="AC276" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD276" t="n">
@@ -34257,7 +34257,7 @@
       </c>
       <c r="AC277" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD277" t="n">
@@ -34379,7 +34379,7 @@
       </c>
       <c r="AC278" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD278" t="n">
@@ -34623,7 +34623,7 @@
       </c>
       <c r="AC280" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD280" t="n">
@@ -34745,7 +34745,7 @@
       </c>
       <c r="AC281" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD281" t="n">
@@ -34989,7 +34989,7 @@
       </c>
       <c r="AC283" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD283" t="n">
@@ -35111,7 +35111,7 @@
       </c>
       <c r="AC284" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD284" t="n">
@@ -35233,7 +35233,7 @@
       </c>
       <c r="AC285" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD285" t="n">
@@ -35599,7 +35599,7 @@
       </c>
       <c r="AC288" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD288" t="n">
@@ -35843,7 +35843,7 @@
       </c>
       <c r="AC290" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD290" t="n">
@@ -35965,7 +35965,7 @@
       </c>
       <c r="AC291" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD291" t="n">
@@ -36453,7 +36453,7 @@
       </c>
       <c r="AC295" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD295" t="n">
@@ -36575,7 +36575,7 @@
       </c>
       <c r="AC296" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD296" t="n">
@@ -36697,7 +36697,7 @@
       </c>
       <c r="AC297" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD297" t="n">
@@ -36819,7 +36819,7 @@
       </c>
       <c r="AC298" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD298" t="n">
@@ -36941,7 +36941,7 @@
       </c>
       <c r="AC299" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD299" t="n">
@@ -37429,7 +37429,7 @@
       </c>
       <c r="AC303" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD303" t="n">
@@ -37551,7 +37551,7 @@
       </c>
       <c r="AC304" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD304" t="n">
@@ -37673,7 +37673,7 @@
       </c>
       <c r="AC305" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD305" t="n">
@@ -37917,7 +37917,7 @@
       </c>
       <c r="AC307" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD307" t="n">
@@ -38161,7 +38161,7 @@
       </c>
       <c r="AC309" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD309" t="n">
@@ -38283,7 +38283,7 @@
       </c>
       <c r="AC310" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD310" t="n">
@@ -38405,7 +38405,7 @@
       </c>
       <c r="AC311" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD311" t="n">
@@ -38527,7 +38527,7 @@
       </c>
       <c r="AC312" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD312" t="n">
@@ -38649,7 +38649,7 @@
       </c>
       <c r="AC313" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD313" t="n">
@@ -38771,7 +38771,7 @@
       </c>
       <c r="AC314" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD314" t="n">
@@ -38893,7 +38893,7 @@
       </c>
       <c r="AC315" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD315" t="n">
@@ -39015,7 +39015,7 @@
       </c>
       <c r="AC316" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD316" t="n">
@@ -39137,7 +39137,7 @@
       </c>
       <c r="AC317" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD317" t="n">
@@ -39259,7 +39259,7 @@
       </c>
       <c r="AC318" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD318" t="n">
@@ -39381,7 +39381,7 @@
       </c>
       <c r="AC319" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD319" t="n">
@@ -39503,7 +39503,7 @@
       </c>
       <c r="AC320" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD320" t="n">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="AC322" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD322" t="n">
@@ -39991,7 +39991,7 @@
       </c>
       <c r="AC324" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD324" t="n">
@@ -40113,7 +40113,7 @@
       </c>
       <c r="AC325" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD325" t="n">
@@ -40235,7 +40235,7 @@
       </c>
       <c r="AC326" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD326" t="n">
@@ -40601,7 +40601,7 @@
       </c>
       <c r="AC329" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD329" t="n">
@@ -41089,7 +41089,7 @@
       </c>
       <c r="AC333" t="inlineStr">
         <is>
-          <t>inactive: Stage-2 vertex already smoothest</t>
+          <t>inactive: multiplicity detected; no reduction above the activity threshold</t>
         </is>
       </c>
       <c r="AD333" t="n">
@@ -41211,7 +41211,7 @@
       </c>
       <c r="AC334" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD334" t="n">
@@ -41333,7 +41333,7 @@
       </c>
       <c r="AC335" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD335" t="n">
@@ -41699,7 +41699,7 @@
       </c>
       <c r="AC338" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD338" t="n">
@@ -41821,7 +41821,7 @@
       </c>
       <c r="AC339" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD339" t="n">
@@ -41943,7 +41943,7 @@
       </c>
       <c r="AC340" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD340" t="n">
@@ -42065,7 +42065,7 @@
       </c>
       <c r="AC341" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD341" t="n">
@@ -42187,7 +42187,7 @@
       </c>
       <c r="AC342" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD342" t="n">
@@ -42309,7 +42309,7 @@
       </c>
       <c r="AC343" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD343" t="n">
@@ -42431,7 +42431,7 @@
       </c>
       <c r="AC344" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD344" t="n">
@@ -42553,7 +42553,7 @@
       </c>
       <c r="AC345" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD345" t="n">
@@ -42675,7 +42675,7 @@
       </c>
       <c r="AC346" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD346" t="n">
@@ -42797,7 +42797,7 @@
       </c>
       <c r="AC347" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD347" t="n">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="AC348" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD348" t="n">
@@ -43041,7 +43041,7 @@
       </c>
       <c r="AC349" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD349" t="n">
@@ -43163,7 +43163,7 @@
       </c>
       <c r="AC350" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD350" t="n">
@@ -43285,7 +43285,7 @@
       </c>
       <c r="AC351" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD351" t="n">
@@ -43407,7 +43407,7 @@
       </c>
       <c r="AC352" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD352" t="n">
@@ -43529,7 +43529,7 @@
       </c>
       <c r="AC353" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD353" t="n">
@@ -43651,7 +43651,7 @@
       </c>
       <c r="AC354" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD354" t="n">
@@ -43773,7 +43773,7 @@
       </c>
       <c r="AC355" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD355" t="n">
@@ -43895,7 +43895,7 @@
       </c>
       <c r="AC356" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD356" t="n">
@@ -44017,7 +44017,7 @@
       </c>
       <c r="AC357" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD357" t="n">
@@ -44139,7 +44139,7 @@
       </c>
       <c r="AC358" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD358" t="n">
@@ -44261,7 +44261,7 @@
       </c>
       <c r="AC359" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD359" t="n">
@@ -44383,7 +44383,7 @@
       </c>
       <c r="AC360" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD360" t="n">
@@ -44505,7 +44505,7 @@
       </c>
       <c r="AC361" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD361" t="n">
@@ -44749,7 +44749,7 @@
       </c>
       <c r="AC363" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD363" t="n">
@@ -44871,7 +44871,7 @@
       </c>
       <c r="AC364" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD364" t="n">
@@ -44993,7 +44993,7 @@
       </c>
       <c r="AC365" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD365" t="n">
@@ -45237,7 +45237,7 @@
       </c>
       <c r="AC367" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD367" t="n">
@@ -45359,7 +45359,7 @@
       </c>
       <c r="AC368" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD368" t="n">
@@ -45481,7 +45481,7 @@
       </c>
       <c r="AC369" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD369" t="n">
@@ -45603,7 +45603,7 @@
       </c>
       <c r="AC370" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD370" t="n">
@@ -45725,7 +45725,7 @@
       </c>
       <c r="AC371" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD371" t="n">
@@ -45847,7 +45847,7 @@
       </c>
       <c r="AC372" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD372" t="n">
@@ -45969,7 +45969,7 @@
       </c>
       <c r="AC373" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD373" t="n">
@@ -46091,7 +46091,7 @@
       </c>
       <c r="AC374" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD374" t="n">
@@ -46213,7 +46213,7 @@
       </c>
       <c r="AC375" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD375" t="n">
@@ -46335,7 +46335,7 @@
       </c>
       <c r="AC376" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD376" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="AC377" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD377" t="n">
@@ -46579,7 +46579,7 @@
       </c>
       <c r="AC378" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD378" t="n">
@@ -46701,7 +46701,7 @@
       </c>
       <c r="AC379" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD379" t="n">
@@ -46823,7 +46823,7 @@
       </c>
       <c r="AC380" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD380" t="n">
@@ -46945,7 +46945,7 @@
       </c>
       <c r="AC381" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD381" t="n">
@@ -47067,7 +47067,7 @@
       </c>
       <c r="AC382" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD382" t="n">
@@ -47189,7 +47189,7 @@
       </c>
       <c r="AC383" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD383" t="n">
@@ -47311,7 +47311,7 @@
       </c>
       <c r="AC384" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD384" t="n">
@@ -47433,7 +47433,7 @@
       </c>
       <c r="AC385" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD385" t="n">
@@ -47555,7 +47555,7 @@
       </c>
       <c r="AC386" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD386" t="n">
@@ -47677,7 +47677,7 @@
       </c>
       <c r="AC387" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD387" t="n">
@@ -47799,7 +47799,7 @@
       </c>
       <c r="AC388" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD388" t="n">
@@ -47921,7 +47921,7 @@
       </c>
       <c r="AC389" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD389" t="n">
@@ -48043,7 +48043,7 @@
       </c>
       <c r="AC390" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD390" t="n">
@@ -48165,7 +48165,7 @@
       </c>
       <c r="AC391" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD391" t="n">
@@ -48287,7 +48287,7 @@
       </c>
       <c r="AC392" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD392" t="n">
@@ -48409,7 +48409,7 @@
       </c>
       <c r="AC393" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD393" t="n">
@@ -48531,7 +48531,7 @@
       </c>
       <c r="AC394" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD394" t="n">
@@ -48653,7 +48653,7 @@
       </c>
       <c r="AC395" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD395" t="n">
@@ -48775,7 +48775,7 @@
       </c>
       <c r="AC396" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD396" t="n">
@@ -48897,7 +48897,7 @@
       </c>
       <c r="AC397" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD397" t="n">
@@ -49019,7 +49019,7 @@
       </c>
       <c r="AC398" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD398" t="n">
@@ -49141,7 +49141,7 @@
       </c>
       <c r="AC399" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD399" t="n">
@@ -49263,7 +49263,7 @@
       </c>
       <c r="AC400" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD400" t="n">
@@ -49385,7 +49385,7 @@
       </c>
       <c r="AC401" t="inlineStr">
         <is>
-          <t>redundant: Stage-2 optimum unique</t>
+          <t>inactive: multiplicity not detected</t>
         </is>
       </c>
       <c r="AD401" t="n">
